--- a/temp/espacios_2025-11-16.xlsx
+++ b/temp/espacios_2025-11-16.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\BD3\Project\Proyecto-DB3\temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4449CA1-F9DC-4395-B425-DD1921F80F6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75A9B43A-F91D-42EF-AA13-F081A991D23C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28690" yWindow="-110" windowWidth="29020" windowHeight="15700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Espacios" sheetId="1" r:id="rId1"/>
